--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,33 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -653,16 +626,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -676,16 +652,19 @@
         <v>14</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -699,16 +678,19 @@
         <v>17</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>17</v>
       </c>
-      <c r="E4">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -722,16 +704,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -787,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -822,7 +807,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,7 +833,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -865,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -914,75 +899,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920317</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920326</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20222.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -772,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -798,16 +807,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -824,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -859,7 +868,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -899,6 +908,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920317</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
